--- a/backtest_runs/20260410_193731/by_symbol/MQTM/MQTM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MQTM/MQTM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-8038.139999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>91961.86</v>
@@ -679,7 +679,7 @@
         <v>-8268.900000000009</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>84462.15999999999</v>
@@ -817,7 +817,7 @@
         <v>-1923</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>82539.15999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-9922.679999999993</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>95461.72</v>
@@ -1139,7 +1139,7 @@
         <v>-9038.099999999991</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>86692.84</v>
@@ -1185,7 +1185,7 @@
         <v>-4269.059999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>82423.78</v>
@@ -1415,7 +1415,7 @@
         <v>-3884.460000000006</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>89654.25999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-7961.220000000001</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>81693.03999999999</v>
@@ -1507,7 +1507,7 @@
         <v>-999.9600000000061</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>80693.07999999999</v>
@@ -1599,7 +1599,7 @@
         <v>-4076.759999999995</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>78654.7</v>
